--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_MT.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_MT.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rd0dab8c2f4bf40e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R53aa801d0da04367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R03b95cd5138b4ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rc77302cd3e4146f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R48d4355da2da4091"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R3ca647118ee6449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Reb07c524047e4511"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R4b208fb42e084996"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R1be2b728e1e34755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Re3d1a03dc52c4493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R0da2c17b7c8644d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R1e304fea795d46d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R9c1695e596ae4b16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R114c016df15c45e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R85347ee5a40b4af2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rbcb3558365a34a92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R2de57b8355bd4a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R05cf33edfb174184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R62f73b56c784483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R86ba37530a694628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rfff95acec6da459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rda24eff11eb347c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rd2ba0d6302894325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rc560c514dda448ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R08c9fd8a9daa4396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R3dfb3196d81e44e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R1fce6259175b40bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rbaa6480dcdff4872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R51ce420438974fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Ree6d3e880391470b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R50dacd17ecbc48a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Ra69fbf8a563743e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rfcd87a665afa4364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rf9e378ade5b647bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R2a90142e9ffa4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R520d3c363b9846c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Ra31e1b08aa024d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R51653be9591949a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rdc7e2ccdbe8a4921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rc1b35c4858844cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rcdd738a295d84494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R8393376ee53f4378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R42681981df66460a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2771,6 +2772,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>リタ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・太白派</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
